--- a/docs/build/lakeshore-enterprise-context/source/05_treasury_kyriba/bank_fee_baseline.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/05_treasury_kyriba/bank_fee_baseline.xlsx
@@ -478,13 +478,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.23</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>3437</v>
+        <v>2268</v>
       </c>
       <c r="D3" t="n">
-        <v>0.75</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="4">
@@ -494,13 +494,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>3026</v>
+        <v>6695</v>
       </c>
       <c r="D4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="5">
@@ -510,13 +510,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.85</v>
+        <v>0.22</v>
       </c>
       <c r="C5" t="n">
-        <v>5137</v>
+        <v>7884</v>
       </c>
       <c r="D5" t="n">
-        <v>0.82</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="6">
@@ -526,13 +526,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="C6" t="n">
-        <v>1361</v>
+        <v>1483</v>
       </c>
       <c r="D6" t="n">
-        <v>0.76</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="7">
@@ -542,13 +542,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.37</v>
+        <v>2.91</v>
       </c>
       <c r="C7" t="n">
-        <v>6639</v>
+        <v>6805</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="8">
@@ -558,13 +558,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.83</v>
+        <v>1.17</v>
       </c>
       <c r="C8" t="n">
-        <v>8382</v>
+        <v>631</v>
       </c>
       <c r="D8" t="n">
-        <v>0.68</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="9">
@@ -574,13 +574,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.92</v>
+        <v>1.46</v>
       </c>
       <c r="C9" t="n">
-        <v>5704</v>
+        <v>4473</v>
       </c>
       <c r="D9" t="n">
-        <v>0.73</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="10">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.14</v>
+        <v>0.75</v>
       </c>
       <c r="C10" t="n">
-        <v>3879</v>
+        <v>1891</v>
       </c>
       <c r="D10" t="n">
-        <v>0.47</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11">
@@ -606,13 +606,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.8</v>
+        <v>0.67</v>
       </c>
       <c r="C11" t="n">
-        <v>8009</v>
+        <v>7521</v>
       </c>
       <c r="D11" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="12">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.42</v>
+        <v>1.09</v>
       </c>
       <c r="C12" t="n">
-        <v>3461</v>
+        <v>4934</v>
       </c>
       <c r="D12" t="n">
-        <v>0.28</v>
+        <v>0.53</v>
       </c>
     </row>
   </sheetData>
